--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19107" uniqueCount="1896">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19107" uniqueCount="1895">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -848,7 +848,7 @@
     <t>OpenELIS Observation</t>
   </si>
   <si>
-    <t>A Observation Resource used for FHIR Exchange</t>
+    <t>An Observation Resource used for FHIR Exchange</t>
   </si>
   <si>
     <t>Observation</t>
@@ -1253,8 +1253,8 @@
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiminginstant</t>
+    <t xml:space="preserve">dateTime
+</t>
   </si>
   <si>
     <t>Clinically relevant time/time-period for observation</t>
@@ -1288,7 +1288,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://digi-uw.github.io/openelis-global-ig/StructureDefinition/open-elispractitioner)
 </t>
   </si>
   <si>
@@ -1302,362 +1302,366 @@
   </si>
   <si>
     <t>Observation.value[x]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Actual result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+  </si>
+  <si>
+    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-7
+</t>
+  </si>
+  <si>
+    <t>Observation.dataAbsentReason</t>
+  </si>
+  <si>
+    <t>Why the result is missing</t>
+  </si>
+  <si>
+    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
+  </si>
+  <si>
+    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
+The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
+  </si>
+  <si>
+    <t>For many results it is necessary to handle exceptional values in measurements.</t>
+  </si>
+  <si>
+    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-6
+</t>
+  </si>
+  <si>
+    <t>Observation.interpretation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Abnormal Flag
+</t>
+  </si>
+  <si>
+    <t>High, low, normal, etc.</t>
+  </si>
+  <si>
+    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
+  </si>
+  <si>
+    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
+  </si>
+  <si>
+    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
+  </si>
+  <si>
+    <t>Codes identifying interpretations of observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+  </si>
+  <si>
+    <t>Observation.note</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annotation
+</t>
+  </si>
+  <si>
+    <t>Comments about the observation</t>
+  </si>
+  <si>
+    <t>Comments about the observation or the results.</t>
+  </si>
+  <si>
+    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
+  </si>
+  <si>
+    <t>Need to be able to provide free text additional information.</t>
+  </si>
+  <si>
+    <t>Observation.bodySite</t>
+  </si>
+  <si>
+    <t>Observed body part</t>
+  </si>
+  <si>
+    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
+If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
+  </si>
+  <si>
+    <t>Codes describing anatomical locations. May include laterality.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+  </si>
+  <si>
+    <t>Observation.method</t>
+  </si>
+  <si>
+    <t>How it was done</t>
+  </si>
+  <si>
+    <t>Indicates the mechanism used to perform the observation.</t>
+  </si>
+  <si>
+    <t>Only used if not implicit in code for Observation.code.</t>
+  </si>
+  <si>
+    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
+  </si>
+  <si>
+    <t>Methods for simple observations.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+  </si>
+  <si>
+    <t>Observation.specimen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Specimen)
+</t>
+  </si>
+  <si>
+    <t>Specimen used for this observation</t>
+  </si>
+  <si>
+    <t>The specimen that was used when this observation was made.</t>
+  </si>
+  <si>
+    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
+  </si>
+  <si>
+    <t>Observation.device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
+</t>
+  </si>
+  <si>
+    <t>(Measurement) Device</t>
+  </si>
+  <si>
+    <t>The device used to generate the observation data.</t>
+  </si>
+  <si>
+    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange</t>
+  </si>
+  <si>
+    <t>Provides guide for interpretation</t>
+  </si>
+  <si>
+    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
+  </si>
+  <si>
+    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
+  </si>
+  <si>
+    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.id</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.extension</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.low</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity {SimpleQuantity}
+</t>
+  </si>
+  <si>
+    <t>Low Range, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">obs-3
+</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.high</t>
+  </si>
+  <si>
+    <t>High Range, if relevant</t>
+  </si>
+  <si>
+    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.type</t>
+  </si>
+  <si>
+    <t>Reference range qualifier</t>
+  </si>
+  <si>
+    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
+  </si>
+  <si>
+    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
+  </si>
+  <si>
+    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
+  </si>
+  <si>
+    <t>Code for the meaning of a reference range.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.appliesTo</t>
+  </si>
+  <si>
+    <t>Reference range population</t>
+  </si>
+  <si>
+    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
+  </si>
+  <si>
+    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
+  </si>
+  <si>
+    <t>Need to be able to identify the target population for proper interpretation.</t>
+  </si>
+  <si>
+    <t>Codes identifying the population the reference range applies to.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.age</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Range
+</t>
+  </si>
+  <si>
+    <t>Applicable age range, if relevant</t>
+  </si>
+  <si>
+    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
+  </si>
+  <si>
+    <t>Some analytes vary greatly over age.</t>
+  </si>
+  <si>
+    <t>Observation.referenceRange.text</t>
+  </si>
+  <si>
+    <t>Text based reference range in an observation</t>
+  </si>
+  <si>
+    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
+  </si>
+  <si>
+    <t>Observation.hasMember</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+</t>
+  </si>
+  <si>
+    <t>Related resource that belongs to the Observation group</t>
+  </si>
+  <si>
+    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+  </si>
+  <si>
+    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
+  </si>
+  <si>
+    <t>Observation.derivedFrom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+</t>
+  </si>
+  <si>
+    <t>Related measurements the observation is made from</t>
+  </si>
+  <si>
+    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+  </si>
+  <si>
+    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
+  </si>
+  <si>
+    <t>Observation.component</t>
+  </si>
+  <si>
+    <t>Component results</t>
+  </si>
+  <si>
+    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
+  </si>
+  <si>
+    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
+  </si>
+  <si>
+    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
+  </si>
+  <si>
+    <t>Observation.component.id</t>
+  </si>
+  <si>
+    <t>Observation.component.extension</t>
+  </si>
+  <si>
+    <t>Observation.component.modifierExtension</t>
+  </si>
+  <si>
+    <t>Observation.component.code</t>
+  </si>
+  <si>
+    <t>Type of component observation (code / type)</t>
+  </si>
+  <si>
+    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
+  </si>
+  <si>
+    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>Observation.component.value[x]</t>
   </si>
   <si>
     <t>Quantity
 CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
-    <t>Actual result</t>
-  </si>
-  <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
-  </si>
-  <si>
-    <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>An observation exists to have a value, though it might not if it is in error, or if it represents a group of observations.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-7
-</t>
-  </si>
-  <si>
-    <t>Observation.dataAbsentReason</t>
-  </si>
-  <si>
-    <t>Why the result is missing</t>
-  </si>
-  <si>
-    <t>Provides a reason why the expected value in the element Observation.value[x] is missing.</t>
-  </si>
-  <si>
-    <t>Null or exceptional values can be represented two ways in FHIR Observations.  One way is to simply include them in the value set and represent the exceptions in the value.  For example, measurement values for a serology test could be  "detected", "not detected", "inconclusive", or  "specimen unsatisfactory".   
-The alternate way is to use the value element for actual observations and use the explicit dataAbsentReason element to record exceptional values.  For example, the dataAbsentReason code "error" could be used when the measurement was not completed. Note that an observation may only be reported if there are values to report. For example differential cell counts values may be reported only when &gt; 0.  Because of these options, use-case agreements are required to interpret general observations for null or exceptional values.</t>
-  </si>
-  <si>
-    <t>For many results it is necessary to handle exceptional values in measurements.</t>
-  </si>
-  <si>
-    <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-6
-</t>
-  </si>
-  <si>
-    <t>Observation.interpretation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abnormal Flag
-</t>
-  </si>
-  <si>
-    <t>High, low, normal, etc.</t>
-  </si>
-  <si>
-    <t>A categorical assessment of an observation value.  For example, high, low, normal.</t>
-  </si>
-  <si>
-    <t>Historically used for laboratory results (known as 'abnormal flag' ),  its use extends to other use cases where coded interpretations  are relevant.  Often reported as one or more simple compact codes this element is often placed adjacent to the result value in reports and flow sheets to signal the meaning/normalcy status of the result.</t>
-  </si>
-  <si>
-    <t>For some results, particularly numeric results, an interpretation is necessary to fully understand the significance of a result.</t>
-  </si>
-  <si>
-    <t>Codes identifying interpretations of observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
-  </si>
-  <si>
-    <t>Observation.note</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annotation
-</t>
-  </si>
-  <si>
-    <t>Comments about the observation</t>
-  </si>
-  <si>
-    <t>Comments about the observation or the results.</t>
-  </si>
-  <si>
-    <t>May include general statements about the observation, or statements about significant, unexpected or unreliable results values, or information about its source when relevant to its interpretation.</t>
-  </si>
-  <si>
-    <t>Need to be able to provide free text additional information.</t>
-  </si>
-  <si>
-    <t>Observation.bodySite</t>
-  </si>
-  <si>
-    <t>Observed body part</t>
-  </si>
-  <si>
-    <t>Indicates the site on the subject's body where the observation was made (i.e. the target site).</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code found in Observation.code.  In many systems, this may be represented as a related observation instead of an inline component.   
-If the use case requires BodySite to be handled as a separate resource (e.g. to identify and track separately) then use the standard extension[ bodySite](http://hl7.org/fhir/R4/extension-bodysite.html).</t>
-  </si>
-  <si>
-    <t>Codes describing anatomical locations. May include laterality.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
-  </si>
-  <si>
-    <t>Observation.method</t>
-  </si>
-  <si>
-    <t>How it was done</t>
-  </si>
-  <si>
-    <t>Indicates the mechanism used to perform the observation.</t>
-  </si>
-  <si>
-    <t>Only used if not implicit in code for Observation.code.</t>
-  </si>
-  <si>
-    <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
-  </si>
-  <si>
-    <t>Methods for simple observations.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
-  </si>
-  <si>
-    <t>Observation.specimen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Specimen)
-</t>
-  </si>
-  <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
-  </si>
-  <si>
-    <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
-  </si>
-  <si>
-    <t>Observation.device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
-</t>
-  </si>
-  <si>
-    <t>(Measurement) Device</t>
-  </si>
-  <si>
-    <t>The device used to generate the observation data.</t>
-  </si>
-  <si>
-    <t>Note that this is not meant to represent a device involved in the transmission of the result, e.g., a gateway.  Such devices may be documented using the Provenance resource where relevant.</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange</t>
-  </si>
-  <si>
-    <t>Provides guide for interpretation</t>
-  </si>
-  <si>
-    <t>Guidance on how to interpret the value by comparison to a normal or recommended range.  Multiple reference ranges are interpreted as an "OR".   In other words, to represent two distinct target populations, two `referenceRange` elements would be used.</t>
-  </si>
-  <si>
-    <t>Most observations only have one generic reference range. Systems MAY choose to restrict to only supplying the relevant reference range based on knowledge about the patient (e.g., specific to the patient's age, gender, weight and other factors), but this might not be possible or appropriate. Whenever more than one reference range is supplied, the differences between them SHOULD be provided in the reference range and/or age properties.</t>
-  </si>
-  <si>
-    <t>Knowing what values are considered "normal" can help evaluate the significance of a particular result. Need to be able to provide multiple reference ranges for different contexts.</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-obs-3:Must have at least a low or a high or text {low.exists() or high.exists() or text.exists()}</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.id</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.extension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.low</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
-</t>
-  </si>
-  <si>
-    <t>Low Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the low bound of the reference range.  The low bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the low bound is omitted,  it is assumed to be meaningless (e.g. reference range is &lt;=2.3).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">obs-3
-</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.high</t>
-  </si>
-  <si>
-    <t>High Range, if relevant</t>
-  </si>
-  <si>
-    <t>The value of the high bound of the reference range.  The high bound of the reference range endpoint is inclusive of the value (e.g.  reference range is &gt;=5 - &lt;=9). If the high bound is omitted,  it is assumed to be meaningless (e.g. reference range is &gt;= 2.3).</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.type</t>
-  </si>
-  <si>
-    <t>Reference range qualifier</t>
-  </si>
-  <si>
-    <t>Codes to indicate the what part of the targeted reference population it applies to. For example, the normal or therapeutic range.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal range is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to say what kind of reference range this is - normal, recommended, therapeutic, etc.,  - for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Code for the meaning of a reference range.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.appliesTo</t>
-  </si>
-  <si>
-    <t>Reference range population</t>
-  </si>
-  <si>
-    <t>Codes to indicate the target population this reference range applies to.  For example, a reference range may be based on the normal population or a particular sex or race.  Multiple `appliesTo`  are interpreted as an "AND" of the target populations.  For example, to represent a target population of African American females, both a code of female and a code for African American would be used.</t>
-  </si>
-  <si>
-    <t>This SHOULD be populated if there is more than one range.  If this element is not present then the normal population is assumed.</t>
-  </si>
-  <si>
-    <t>Need to be able to identify the target population for proper interpretation.</t>
-  </si>
-  <si>
-    <t>Codes identifying the population the reference range applies to.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.age</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Range
-</t>
-  </si>
-  <si>
-    <t>Applicable age range, if relevant</t>
-  </si>
-  <si>
-    <t>The age at which this reference range is applicable. This is a neonatal age (e.g. number of weeks at term) if the meaning says so.</t>
-  </si>
-  <si>
-    <t>Some analytes vary greatly over age.</t>
-  </si>
-  <si>
-    <t>Observation.referenceRange.text</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation</t>
-  </si>
-  <si>
-    <t>Text based reference range in an observation which may be used when a quantitative range is not appropriate for an observation.  An example would be a reference value of "Negative" or a list or table of "normals".</t>
-  </si>
-  <si>
-    <t>Observation.hasMember</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
-</t>
-  </si>
-  <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
-  </si>
-  <si>
-    <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
-  </si>
-  <si>
-    <t>Observation.derivedFrom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
-</t>
-  </si>
-  <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
-  </si>
-  <si>
-    <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
-  </si>
-  <si>
-    <t>Observation.component</t>
-  </si>
-  <si>
-    <t>Component results</t>
-  </si>
-  <si>
-    <t>Some observations have multiple component observations.  These component observations are expressed as separate code value pairs that share the same attributes.  Examples include systolic and diastolic component observations for blood pressure measurement and multiple component observations for genetics observations.</t>
-  </si>
-  <si>
-    <t>For a discussion on the ways Observations can be assembled in groups together see [Notes](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
-  </si>
-  <si>
-    <t>Component observations share the same attributes in the Observation resource as the primary observation and are always treated a part of a single observation (they are not separable).   However, the reference range for the primary observation value is not inherited by the component values and is required when appropriate for each component observation.</t>
-  </si>
-  <si>
-    <t>Observation.component.id</t>
-  </si>
-  <si>
-    <t>Observation.component.extension</t>
-  </si>
-  <si>
-    <t>Observation.component.modifierExtension</t>
-  </si>
-  <si>
-    <t>Observation.component.code</t>
-  </si>
-  <si>
-    <t>Type of component observation (code / type)</t>
-  </si>
-  <si>
-    <t>Describes what was observed. Sometimes this is called the observation "code".</t>
-  </si>
-  <si>
-    <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
-  </si>
-  <si>
-    <t>Observation.component.value[x]</t>
-  </si>
-  <si>
     <t>Actual component result</t>
   </si>
   <si>
@@ -2011,10 +2015,6 @@
   </si>
   <si>
     <t>Specimen.receivedTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
   </si>
   <si>
     <t>The time when specimen was received for processing</t>
@@ -5065,10 +5065,6 @@
   <si>
     <t>author
 orderer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(http://digi-uw.github.io/openelis-global-ig/StructureDefinition/open-elispractitioner)
-</t>
   </si>
   <si>
     <t>Who/what is requesting service</t>
@@ -6344,7 +6340,7 @@
         <v>2</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
     </row>
     <row r="43">
@@ -6352,7 +6348,7 @@
         <v>4</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="44">
@@ -6368,7 +6364,7 @@
         <v>8</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="46">
@@ -6376,7 +6372,7 @@
         <v>10</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
     </row>
     <row r="47">
@@ -6420,7 +6416,7 @@
         <v>20</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="53">
@@ -6456,7 +6452,7 @@
         <v>28</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
     </row>
     <row r="58">
@@ -6464,7 +6460,7 @@
         <v>30</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="59">
@@ -7256,7 +7252,7 @@
         <v>2</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="163">
@@ -7264,7 +7260,7 @@
         <v>4</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>1695</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="164">
@@ -7280,7 +7276,7 @@
         <v>8</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>1696</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="166">
@@ -7288,7 +7284,7 @@
         <v>10</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>1697</v>
+        <v>1696</v>
       </c>
     </row>
     <row r="167">
@@ -7332,7 +7328,7 @@
         <v>20</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>1698</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="173">
@@ -7368,7 +7364,7 @@
         <v>28</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>1699</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="178">
@@ -7376,7 +7372,7 @@
         <v>30</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1700</v>
+        <v>1699</v>
       </c>
     </row>
     <row r="179">
@@ -17466,16 +17462,16 @@
         <v>80</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>413</v>
+        <v>526</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N96" t="s" s="2">
         <v>415</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>417</v>
@@ -17547,10 +17543,10 @@
         <v>263</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D97" s="2"/>
       <c r="E97" t="s" s="2">
@@ -17576,13 +17572,13 @@
         <v>172</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="O97" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>423</v>
@@ -17634,7 +17630,7 @@
         <v>19</v>
       </c>
       <c r="AG97" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AH97" t="s" s="2">
         <v>72</v>
@@ -17654,10 +17650,10 @@
         <v>263</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="D98" s="2"/>
       <c r="E98" t="s" s="2">
@@ -17741,7 +17737,7 @@
         <v>19</v>
       </c>
       <c r="AG98" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="AH98" t="s" s="2">
         <v>72</v>
@@ -17761,10 +17757,10 @@
         <v>263</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C99" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D99" s="2"/>
       <c r="E99" t="s" s="2">
@@ -17790,10 +17786,10 @@
         <v>74</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O99" t="s" s="2">
         <v>467</v>
@@ -17848,7 +17844,7 @@
         <v>19</v>
       </c>
       <c r="AG99" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AH99" t="s" s="2">
         <v>72</v>
@@ -17865,13 +17861,13 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="C100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="D100" s="2"/>
       <c r="E100" t="s" s="2">
@@ -17897,10 +17893,10 @@
         <v>74</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" s="2"/>
@@ -17951,7 +17947,7 @@
         <v>19</v>
       </c>
       <c r="AG100" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AH100" t="s" s="2">
         <v>72</v>
@@ -17968,13 +17964,13 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="C101" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D101" s="2"/>
       <c r="E101" t="s" s="2">
@@ -18073,13 +18069,13 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="D102" s="2"/>
       <c r="E102" t="s" s="2">
@@ -18176,13 +18172,13 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="D103" s="2"/>
       <c r="E103" t="s" s="2">
@@ -18281,13 +18277,13 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C104" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D104" s="2"/>
       <c r="E104" t="s" s="2">
@@ -18386,13 +18382,13 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D105" s="2"/>
       <c r="E105" t="s" s="2">
@@ -18491,13 +18487,13 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C106" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="D106" s="2"/>
       <c r="E106" t="s" s="2">
@@ -18596,13 +18592,13 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C107" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D107" s="2"/>
       <c r="E107" t="s" s="2">
@@ -18701,13 +18697,13 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="D108" s="2"/>
       <c r="E108" t="s" s="2">
@@ -18808,13 +18804,13 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D109" s="2"/>
       <c r="E109" t="s" s="2">
@@ -18840,10 +18836,10 @@
         <v>135</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" s="2"/>
@@ -18892,7 +18888,7 @@
         <v>288</v>
       </c>
       <c r="AG109" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH109" t="s" s="2">
         <v>72</v>
@@ -18909,13 +18905,13 @@
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D110" t="s" s="2">
         <v>290</v>
@@ -18943,10 +18939,10 @@
         <v>135</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" s="2"/>
@@ -18997,7 +18993,7 @@
         <v>19</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>72</v>
@@ -19014,13 +19010,13 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C111" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D111" s="2"/>
       <c r="E111" t="s" s="2">
@@ -19117,13 +19113,13 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C112" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D112" s="2"/>
       <c r="E112" t="s" s="2">
@@ -19222,13 +19218,13 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C113" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="D113" s="2"/>
       <c r="E113" t="s" s="2">
@@ -19329,13 +19325,13 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C114" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="D114" s="2"/>
       <c r="E114" t="s" s="2">
@@ -19436,13 +19432,13 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C115" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D115" s="2"/>
       <c r="E115" t="s" s="2">
@@ -19487,7 +19483,7 @@
         <v>19</v>
       </c>
       <c r="T115" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="U115" t="s" s="2">
         <v>322</v>
@@ -19543,13 +19539,13 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C116" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D116" s="2"/>
       <c r="E116" t="s" s="2">
@@ -19648,13 +19644,13 @@
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C117" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="D117" s="2"/>
       <c r="E117" t="s" s="2">
@@ -19751,13 +19747,13 @@
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="D118" s="2"/>
       <c r="E118" t="s" s="2">
@@ -19856,13 +19852,13 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="D119" s="2"/>
       <c r="E119" t="s" s="2">
@@ -19888,10 +19884,10 @@
         <v>135</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
@@ -19942,7 +19938,7 @@
         <v>19</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>72</v>
@@ -19959,13 +19955,13 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D120" s="2"/>
       <c r="E120" t="s" s="2">
@@ -20062,13 +20058,13 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C121" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D121" s="2"/>
       <c r="E121" t="s" s="2">
@@ -20167,13 +20163,13 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C122" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="D122" s="2"/>
       <c r="E122" t="s" s="2">
@@ -20274,13 +20270,13 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C123" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="D123" s="2"/>
       <c r="E123" t="s" s="2">
@@ -20381,13 +20377,13 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C124" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D124" s="2"/>
       <c r="E124" t="s" s="2">
@@ -20488,13 +20484,13 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="C125" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="D125" s="2"/>
       <c r="E125" t="s" s="2">
@@ -20593,13 +20589,13 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C126" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="D126" s="2"/>
       <c r="E126" t="s" s="2">
@@ -20696,13 +20692,13 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C127" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D127" s="2"/>
       <c r="E127" t="s" s="2">
@@ -20801,13 +20797,13 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C128" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="D128" s="2"/>
       <c r="E128" t="s" s="2">
@@ -20833,10 +20829,10 @@
         <v>99</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O128" t="s" s="2">
         <v>358</v>
@@ -20868,10 +20864,10 @@
         <v>142</v>
       </c>
       <c r="Z128" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="AA128" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AB128" t="s" s="2">
         <v>19</v>
@@ -20889,7 +20885,7 @@
         <v>19</v>
       </c>
       <c r="AG128" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AH128" t="s" s="2">
         <v>72</v>
@@ -20906,13 +20902,13 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="C129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D129" s="2"/>
       <c r="E129" t="s" s="2">
@@ -20938,13 +20934,13 @@
         <v>172</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="O129" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="P129" s="2"/>
       <c r="Q129" t="s" s="2">
@@ -20973,10 +20969,10 @@
         <v>191</v>
       </c>
       <c r="Z129" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AA129" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="AB129" t="s" s="2">
         <v>19</v>
@@ -20994,7 +20990,7 @@
         <v>19</v>
       </c>
       <c r="AG129" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AH129" t="s" s="2">
         <v>72</v>
@@ -21011,13 +21007,13 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="C130" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D130" s="2"/>
       <c r="E130" t="s" s="2">
@@ -21114,13 +21110,13 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C131" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="D131" s="2"/>
       <c r="E131" t="s" s="2">
@@ -21219,13 +21215,13 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C132" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="D132" s="2"/>
       <c r="E132" t="s" s="2">
@@ -21251,16 +21247,16 @@
         <v>146</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O132" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P132" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Q132" t="s" s="2">
         <v>19</v>
@@ -21309,7 +21305,7 @@
         <v>19</v>
       </c>
       <c r="AG132" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AH132" t="s" s="2">
         <v>72</v>
@@ -21326,13 +21322,13 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="C133" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="D133" s="2"/>
       <c r="E133" t="s" s="2">
@@ -21429,13 +21425,13 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C134" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="D134" s="2"/>
       <c r="E134" t="s" s="2">
@@ -21534,13 +21530,13 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C135" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="D135" s="2"/>
       <c r="E135" t="s" s="2">
@@ -21566,16 +21562,16 @@
         <v>93</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O135" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P135" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Q135" t="s" s="2">
         <v>19</v>
@@ -21624,7 +21620,7 @@
         <v>19</v>
       </c>
       <c r="AG135" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AH135" t="s" s="2">
         <v>72</v>
@@ -21641,13 +21637,13 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="C136" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="D136" s="2"/>
       <c r="E136" t="s" s="2">
@@ -21673,13 +21669,13 @@
         <v>152</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O136" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P136" s="2"/>
       <c r="Q136" t="s" s="2">
@@ -21729,7 +21725,7 @@
         <v>19</v>
       </c>
       <c r="AG136" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AH136" t="s" s="2">
         <v>72</v>
@@ -21746,13 +21742,13 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C137" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D137" s="2"/>
       <c r="E137" t="s" s="2">
@@ -21778,14 +21774,14 @@
         <v>99</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Q137" t="s" s="2">
         <v>19</v>
@@ -21834,7 +21830,7 @@
         <v>19</v>
       </c>
       <c r="AG137" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AH137" t="s" s="2">
         <v>72</v>
@@ -21851,13 +21847,13 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="C138" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="D138" s="2"/>
       <c r="E138" t="s" s="2">
@@ -21883,14 +21879,14 @@
         <v>152</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N138" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Q138" t="s" s="2">
         <v>19</v>
@@ -21939,7 +21935,7 @@
         <v>19</v>
       </c>
       <c r="AG138" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AH138" t="s" s="2">
         <v>72</v>
@@ -21956,13 +21952,13 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="C139" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="D139" s="2"/>
       <c r="E139" t="s" s="2">
@@ -21988,16 +21984,16 @@
         <v>245</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P139" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Q139" t="s" s="2">
         <v>19</v>
@@ -22046,7 +22042,7 @@
         <v>19</v>
       </c>
       <c r="AG139" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AH139" t="s" s="2">
         <v>72</v>
@@ -22063,13 +22059,13 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C140" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="D140" s="2"/>
       <c r="E140" t="s" s="2">
@@ -22095,16 +22091,16 @@
         <v>152</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N140" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O140" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P140" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q140" t="s" s="2">
         <v>19</v>
@@ -22153,7 +22149,7 @@
         <v>19</v>
       </c>
       <c r="AG140" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AH140" t="s" s="2">
         <v>72</v>
@@ -22170,13 +22166,13 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C141" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="D141" s="2"/>
       <c r="E141" t="s" s="2">
@@ -22202,14 +22198,14 @@
         <v>378</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="N141" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="O141" s="2"/>
       <c r="P141" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="Q141" t="s" s="2">
         <v>19</v>
@@ -22258,7 +22254,7 @@
         <v>19</v>
       </c>
       <c r="AG141" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AH141" t="s" s="2">
         <v>72</v>
@@ -22275,13 +22271,13 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="D142" s="2"/>
       <c r="E142" t="s" s="2">
@@ -22304,7 +22300,7 @@
         <v>80</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="M142" t="s" s="2">
         <v>645</v>
@@ -22361,7 +22357,7 @@
         <v>19</v>
       </c>
       <c r="AG142" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="AH142" t="s" s="2">
         <v>72</v>
@@ -22378,7 +22374,7 @@
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B143" t="s" s="2">
         <v>647</v>
@@ -22483,7 +22479,7 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B144" t="s" s="2">
         <v>651</v>
@@ -22588,7 +22584,7 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B145" t="s" s="2">
         <v>655</v>
@@ -22691,7 +22687,7 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B146" t="s" s="2">
         <v>658</v>
@@ -22794,7 +22790,7 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B147" t="s" s="2">
         <v>659</v>
@@ -22899,7 +22895,7 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B148" t="s" s="2">
         <v>660</v>
@@ -23006,7 +23002,7 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B149" t="s" s="2">
         <v>661</v>
@@ -23109,7 +23105,7 @@
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B150" t="s" s="2">
         <v>665</v>
@@ -23138,7 +23134,7 @@
         <v>80</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="M150" t="s" s="2">
         <v>666</v>
@@ -23210,7 +23206,7 @@
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B151" t="s" s="2">
         <v>670</v>
@@ -23241,7 +23237,7 @@
         <v>80</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="M151" t="s" s="2">
         <v>666</v>
@@ -23315,7 +23311,7 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B152" t="s" s="2">
         <v>672</v>
@@ -23418,7 +23414,7 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B153" t="s" s="2">
         <v>676</v>
@@ -23521,7 +23517,7 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B154" t="s" s="2">
         <v>679</v>
@@ -23624,7 +23620,7 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B155" t="s" s="2">
         <v>684</v>
@@ -23729,7 +23725,7 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B156" t="s" s="2">
         <v>688</v>
@@ -23836,7 +23832,7 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B157" t="s" s="2">
         <v>696</v>
@@ -23939,7 +23935,7 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B158" t="s" s="2">
         <v>699</v>
@@ -24042,7 +24038,7 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B159" t="s" s="2">
         <v>700</v>
@@ -24147,7 +24143,7 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B160" t="s" s="2">
         <v>701</v>
@@ -24254,7 +24250,7 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B161" t="s" s="2">
         <v>702</v>
@@ -24357,7 +24353,7 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B162" t="s" s="2">
         <v>705</v>
@@ -24460,7 +24456,7 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B163" t="s" s="2">
         <v>710</v>
@@ -24563,7 +24559,7 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B164" t="s" s="2">
         <v>714</v>
@@ -24666,7 +24662,7 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B165" t="s" s="2">
         <v>718</v>
@@ -24769,7 +24765,7 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B166" t="s" s="2">
         <v>721</v>
@@ -24872,7 +24868,7 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B167" t="s" s="2">
         <v>722</v>
@@ -24977,7 +24973,7 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B168" t="s" s="2">
         <v>723</v>
@@ -25084,7 +25080,7 @@
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B169" t="s" s="2">
         <v>724</v>
@@ -25187,7 +25183,7 @@
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B170" t="s" s="2">
         <v>727</v>
@@ -25290,7 +25286,7 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B171" t="s" s="2">
         <v>730</v>
@@ -25393,7 +25389,7 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B172" t="s" s="2">
         <v>735</v>
@@ -25496,7 +25492,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B173" t="s" s="2">
         <v>738</v>
@@ -25599,7 +25595,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B174" t="s" s="2">
         <v>741</v>
@@ -25702,7 +25698,7 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B175" t="s" s="2">
         <v>747</v>
@@ -25809,7 +25805,7 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B176" t="s" s="2">
         <v>754</v>
@@ -40884,16 +40880,16 @@
         <v>146</v>
       </c>
       <c r="M319" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N319" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O319" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P319" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Q319" t="s" s="2">
         <v>19</v>
@@ -40942,7 +40938,7 @@
         <v>19</v>
       </c>
       <c r="AG319" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AH319" t="s" s="2">
         <v>72</v>
@@ -40991,16 +40987,16 @@
         <v>152</v>
       </c>
       <c r="M320" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N320" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O320" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P320" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q320" t="s" s="2">
         <v>19</v>
@@ -41049,7 +41045,7 @@
         <v>19</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>72</v>
@@ -57651,16 +57647,16 @@
         <v>146</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O478" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P478" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Q478" t="s" s="2">
         <v>19</v>
@@ -57709,7 +57705,7 @@
         <v>19</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>72</v>
@@ -57966,16 +57962,16 @@
         <v>93</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="O481" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="P481" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="Q481" t="s" s="2">
         <v>19</v>
@@ -58024,7 +58020,7 @@
         <v>19</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>72</v>
@@ -58073,13 +58069,13 @@
         <v>152</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="O482" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="P482" s="2"/>
       <c r="Q482" t="s" s="2">
@@ -58129,7 +58125,7 @@
         <v>19</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>72</v>
@@ -58178,14 +58174,14 @@
         <v>99</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="O483" s="2"/>
       <c r="P483" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="Q483" t="s" s="2">
         <v>19</v>
@@ -58234,7 +58230,7 @@
         <v>19</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>72</v>
@@ -58283,14 +58279,14 @@
         <v>152</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="O484" s="2"/>
       <c r="P484" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="Q484" t="s" s="2">
         <v>19</v>
@@ -58339,7 +58335,7 @@
         <v>19</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>72</v>
@@ -58388,16 +58384,16 @@
         <v>245</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="O485" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="P485" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="Q485" t="s" s="2">
         <v>19</v>
@@ -58446,7 +58442,7 @@
         <v>19</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>72</v>
@@ -58495,16 +58491,16 @@
         <v>152</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O486" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P486" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q486" t="s" s="2">
         <v>19</v>
@@ -58553,7 +58549,7 @@
         <v>19</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>72</v>
@@ -59221,7 +59217,7 @@
         <v>80</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="M493" t="s" s="2">
         <v>1627</v>
@@ -59324,16 +59320,16 @@
         <v>80</v>
       </c>
       <c r="L494" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="M494" t="s" s="2">
         <v>1631</v>
       </c>
-      <c r="M494" t="s" s="2">
+      <c r="N494" t="s" s="2">
         <v>1632</v>
       </c>
-      <c r="N494" t="s" s="2">
+      <c r="O494" t="s" s="2">
         <v>1633</v>
-      </c>
-      <c r="O494" t="s" s="2">
-        <v>1634</v>
       </c>
       <c r="P494" s="2"/>
       <c r="Q494" t="s" s="2">
@@ -59403,14 +59399,14 @@
         <v>1467</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
-        <v>1636</v>
+        <v>1635</v>
       </c>
       <c r="F495" s="2"/>
       <c r="G495" t="s" s="2">
@@ -59432,13 +59428,13 @@
         <v>172</v>
       </c>
       <c r="M495" t="s" s="2">
+        <v>1636</v>
+      </c>
+      <c r="N495" t="s" s="2">
         <v>1637</v>
       </c>
-      <c r="N495" t="s" s="2">
+      <c r="O495" t="s" s="2">
         <v>1638</v>
-      </c>
-      <c r="O495" t="s" s="2">
-        <v>1639</v>
       </c>
       <c r="P495" s="2"/>
       <c r="Q495" t="s" s="2">
@@ -59467,11 +59463,11 @@
         <v>191</v>
       </c>
       <c r="Z495" t="s" s="2">
+        <v>1639</v>
+      </c>
+      <c r="AA495" t="s" s="2">
         <v>1640</v>
       </c>
-      <c r="AA495" t="s" s="2">
-        <v>1641</v>
-      </c>
       <c r="AB495" t="s" s="2">
         <v>19</v>
       </c>
@@ -59488,7 +59484,7 @@
         <v>19</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1635</v>
+        <v>1634</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>72</v>
@@ -59508,14 +59504,14 @@
         <v>1467</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
-        <v>1643</v>
+        <v>1642</v>
       </c>
       <c r="F496" s="2"/>
       <c r="G496" t="s" s="2">
@@ -59534,16 +59530,16 @@
         <v>80</v>
       </c>
       <c r="L496" t="s" s="2">
+        <v>1643</v>
+      </c>
+      <c r="M496" t="s" s="2">
         <v>1644</v>
       </c>
-      <c r="M496" t="s" s="2">
+      <c r="N496" t="s" s="2">
         <v>1645</v>
       </c>
-      <c r="N496" t="s" s="2">
+      <c r="O496" t="s" s="2">
         <v>1646</v>
-      </c>
-      <c r="O496" t="s" s="2">
-        <v>1647</v>
       </c>
       <c r="P496" s="2"/>
       <c r="Q496" t="s" s="2">
@@ -59593,7 +59589,7 @@
         <v>19</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1642</v>
+        <v>1641</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>72</v>
@@ -59613,10 +59609,10 @@
         <v>1467</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -59642,10 +59638,10 @@
         <v>172</v>
       </c>
       <c r="M497" t="s" s="2">
+        <v>1648</v>
+      </c>
+      <c r="N497" t="s" s="2">
         <v>1649</v>
-      </c>
-      <c r="N497" t="s" s="2">
-        <v>1650</v>
       </c>
       <c r="O497" s="2"/>
       <c r="P497" s="2"/>
@@ -59675,7 +59671,7 @@
         <v>191</v>
       </c>
       <c r="Z497" t="s" s="2">
-        <v>1651</v>
+        <v>1650</v>
       </c>
       <c r="AA497" t="s" s="2">
         <v>176</v>
@@ -59696,7 +59692,7 @@
         <v>19</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1648</v>
+        <v>1647</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>72</v>
@@ -59716,10 +59712,10 @@
         <v>1467</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -59745,10 +59741,10 @@
         <v>228</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>1649</v>
+        <v>1648</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>1653</v>
+        <v>1652</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -59799,7 +59795,7 @@
         <v>19</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>1652</v>
+        <v>1651</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>72</v>
@@ -59819,10 +59815,10 @@
         <v>1467</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -59848,13 +59844,13 @@
         <v>172</v>
       </c>
       <c r="M499" t="s" s="2">
+        <v>1654</v>
+      </c>
+      <c r="N499" t="s" s="2">
         <v>1655</v>
       </c>
-      <c r="N499" t="s" s="2">
+      <c r="O499" t="s" s="2">
         <v>1656</v>
-      </c>
-      <c r="O499" t="s" s="2">
-        <v>1657</v>
       </c>
       <c r="P499" s="2"/>
       <c r="Q499" t="s" s="2">
@@ -59883,11 +59879,11 @@
         <v>191</v>
       </c>
       <c r="Z499" t="s" s="2">
+        <v>1657</v>
+      </c>
+      <c r="AA499" t="s" s="2">
         <v>1658</v>
       </c>
-      <c r="AA499" t="s" s="2">
-        <v>1659</v>
-      </c>
       <c r="AB499" t="s" s="2">
         <v>19</v>
       </c>
@@ -59904,7 +59900,7 @@
         <v>19</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>1654</v>
+        <v>1653</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>72</v>
@@ -59924,10 +59920,10 @@
         <v>1467</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -59950,16 +59946,16 @@
         <v>80</v>
       </c>
       <c r="L500" t="s" s="2">
+        <v>1660</v>
+      </c>
+      <c r="M500" t="s" s="2">
         <v>1661</v>
       </c>
-      <c r="M500" t="s" s="2">
+      <c r="N500" t="s" s="2">
         <v>1662</v>
       </c>
-      <c r="N500" t="s" s="2">
+      <c r="O500" t="s" s="2">
         <v>1663</v>
-      </c>
-      <c r="O500" t="s" s="2">
-        <v>1664</v>
       </c>
       <c r="P500" s="2"/>
       <c r="Q500" t="s" s="2">
@@ -60009,7 +60005,7 @@
         <v>19</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>72</v>
@@ -60029,10 +60025,10 @@
         <v>1467</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -60055,13 +60051,13 @@
         <v>19</v>
       </c>
       <c r="L501" t="s" s="2">
+        <v>1665</v>
+      </c>
+      <c r="M501" t="s" s="2">
         <v>1666</v>
       </c>
-      <c r="M501" t="s" s="2">
+      <c r="N501" t="s" s="2">
         <v>1667</v>
-      </c>
-      <c r="N501" t="s" s="2">
-        <v>1668</v>
       </c>
       <c r="O501" s="2"/>
       <c r="P501" s="2"/>
@@ -60112,7 +60108,7 @@
         <v>19</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>72</v>
@@ -60132,14 +60128,14 @@
         <v>1467</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="F502" s="2"/>
       <c r="G502" t="s" s="2">
@@ -60161,13 +60157,13 @@
         <v>384</v>
       </c>
       <c r="M502" t="s" s="2">
+        <v>1670</v>
+      </c>
+      <c r="N502" t="s" s="2">
         <v>1671</v>
       </c>
-      <c r="N502" t="s" s="2">
+      <c r="O502" t="s" s="2">
         <v>1672</v>
-      </c>
-      <c r="O502" t="s" s="2">
-        <v>1673</v>
       </c>
       <c r="P502" s="2"/>
       <c r="Q502" t="s" s="2">
@@ -60217,7 +60213,7 @@
         <v>19</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>72</v>
@@ -60237,10 +60233,10 @@
         <v>1467</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -60266,13 +60262,13 @@
         <v>1199</v>
       </c>
       <c r="M503" t="s" s="2">
+        <v>1674</v>
+      </c>
+      <c r="N503" t="s" s="2">
         <v>1675</v>
       </c>
-      <c r="N503" t="s" s="2">
+      <c r="O503" t="s" s="2">
         <v>1676</v>
-      </c>
-      <c r="O503" t="s" s="2">
-        <v>1677</v>
       </c>
       <c r="P503" s="2"/>
       <c r="Q503" t="s" s="2">
@@ -60322,7 +60318,7 @@
         <v>19</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1674</v>
+        <v>1673</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>72</v>
@@ -60342,14 +60338,14 @@
         <v>1467</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
-        <v>1679</v>
+        <v>1678</v>
       </c>
       <c r="F504" s="2"/>
       <c r="G504" t="s" s="2">
@@ -60371,16 +60367,16 @@
         <v>172</v>
       </c>
       <c r="M504" t="s" s="2">
+        <v>1679</v>
+      </c>
+      <c r="N504" t="s" s="2">
         <v>1680</v>
       </c>
-      <c r="N504" t="s" s="2">
+      <c r="O504" t="s" s="2">
         <v>1681</v>
       </c>
-      <c r="O504" t="s" s="2">
+      <c r="P504" t="s" s="2">
         <v>1682</v>
-      </c>
-      <c r="P504" t="s" s="2">
-        <v>1683</v>
       </c>
       <c r="Q504" t="s" s="2">
         <v>19</v>
@@ -60429,7 +60425,7 @@
         <v>19</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1678</v>
+        <v>1677</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>72</v>
@@ -60449,10 +60445,10 @@
         <v>1467</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -60481,7 +60477,7 @@
         <v>49</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="O505" s="2"/>
       <c r="P505" s="2"/>
@@ -60532,7 +60528,7 @@
         <v>19</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>72</v>
@@ -60552,10 +60548,10 @@
         <v>1467</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -60581,10 +60577,10 @@
         <v>152</v>
       </c>
       <c r="M506" t="s" s="2">
+        <v>1686</v>
+      </c>
+      <c r="N506" t="s" s="2">
         <v>1687</v>
-      </c>
-      <c r="N506" t="s" s="2">
-        <v>1688</v>
       </c>
       <c r="O506" s="2"/>
       <c r="P506" s="2"/>
@@ -60635,7 +60631,7 @@
         <v>19</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>72</v>
@@ -60655,10 +60651,10 @@
         <v>1467</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -60681,16 +60677,16 @@
         <v>19</v>
       </c>
       <c r="L507" t="s" s="2">
+        <v>1689</v>
+      </c>
+      <c r="M507" t="s" s="2">
         <v>1690</v>
       </c>
-      <c r="M507" t="s" s="2">
+      <c r="N507" t="s" s="2">
         <v>1691</v>
       </c>
-      <c r="N507" t="s" s="2">
+      <c r="O507" t="s" s="2">
         <v>1692</v>
-      </c>
-      <c r="O507" t="s" s="2">
-        <v>1693</v>
       </c>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
@@ -60740,7 +60736,7 @@
         <v>19</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>72</v>
@@ -60757,13 +60753,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -60789,10 +60785,10 @@
         <v>74</v>
       </c>
       <c r="M508" t="s" s="2">
+        <v>1700</v>
+      </c>
+      <c r="N508" t="s" s="2">
         <v>1701</v>
-      </c>
-      <c r="N508" t="s" s="2">
-        <v>1702</v>
       </c>
       <c r="O508" s="2"/>
       <c r="P508" s="2"/>
@@ -60843,7 +60839,7 @@
         <v>19</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>72</v>
@@ -60855,18 +60851,18 @@
         <v>19</v>
       </c>
       <c r="AK508" t="s" s="2">
-        <v>1703</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -60965,13 +60961,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -61068,13 +61064,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -61173,13 +61169,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -61278,13 +61274,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -61383,13 +61379,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -61488,13 +61484,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -61593,13 +61589,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -61700,13 +61696,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -61732,10 +61728,10 @@
         <v>135</v>
       </c>
       <c r="M517" t="s" s="2">
+        <v>1712</v>
+      </c>
+      <c r="N517" t="s" s="2">
         <v>1713</v>
-      </c>
-      <c r="N517" t="s" s="2">
-        <v>1714</v>
       </c>
       <c r="O517" s="2"/>
       <c r="P517" s="2"/>
@@ -61786,7 +61782,7 @@
         <v>19</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>72</v>
@@ -61803,13 +61799,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -61832,17 +61828,17 @@
         <v>80</v>
       </c>
       <c r="L518" t="s" s="2">
+        <v>1715</v>
+      </c>
+      <c r="M518" t="s" s="2">
         <v>1716</v>
       </c>
-      <c r="M518" t="s" s="2">
+      <c r="N518" t="s" s="2">
         <v>1717</v>
-      </c>
-      <c r="N518" t="s" s="2">
-        <v>1718</v>
       </c>
       <c r="O518" s="2"/>
       <c r="P518" t="s" s="2">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="Q518" t="s" s="2">
         <v>19</v>
@@ -61891,7 +61887,7 @@
         <v>19</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>72</v>
@@ -61908,13 +61904,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -61940,14 +61936,14 @@
         <v>93</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="O519" s="2"/>
       <c r="P519" t="s" s="2">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="Q519" t="s" s="2">
         <v>19</v>
@@ -61996,7 +61992,7 @@
         <v>19</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>72</v>
@@ -62013,13 +62009,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -62045,10 +62041,10 @@
         <v>345</v>
       </c>
       <c r="M520" t="s" s="2">
+        <v>1723</v>
+      </c>
+      <c r="N520" t="s" s="2">
         <v>1724</v>
-      </c>
-      <c r="N520" t="s" s="2">
-        <v>1725</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" s="2"/>
@@ -62099,7 +62095,7 @@
         <v>19</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>72</v>
@@ -62116,13 +62112,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -62148,14 +62144,14 @@
         <v>135</v>
       </c>
       <c r="M521" t="s" s="2">
+        <v>1726</v>
+      </c>
+      <c r="N521" t="s" s="2">
         <v>1727</v>
-      </c>
-      <c r="N521" t="s" s="2">
-        <v>1728</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" t="s" s="2">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="Q521" t="s" s="2">
         <v>19</v>
@@ -62204,7 +62200,7 @@
         <v>19</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>72</v>
@@ -62221,13 +62217,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -62250,19 +62246,19 @@
         <v>80</v>
       </c>
       <c r="L522" t="s" s="2">
+        <v>1730</v>
+      </c>
+      <c r="M522" t="s" s="2">
         <v>1731</v>
       </c>
-      <c r="M522" t="s" s="2">
+      <c r="N522" t="s" s="2">
         <v>1732</v>
       </c>
-      <c r="N522" t="s" s="2">
+      <c r="O522" t="s" s="2">
         <v>1733</v>
       </c>
-      <c r="O522" t="s" s="2">
+      <c r="P522" t="s" s="2">
         <v>1734</v>
-      </c>
-      <c r="P522" t="s" s="2">
-        <v>1735</v>
       </c>
       <c r="Q522" t="s" s="2">
         <v>19</v>
@@ -62311,7 +62307,7 @@
         <v>19</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>72</v>
@@ -62328,13 +62324,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -62360,14 +62356,14 @@
         <v>99</v>
       </c>
       <c r="M523" t="s" s="2">
+        <v>1736</v>
+      </c>
+      <c r="N523" t="s" s="2">
         <v>1737</v>
-      </c>
-      <c r="N523" t="s" s="2">
-        <v>1738</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" t="s" s="2">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="Q523" t="s" s="2">
         <v>19</v>
@@ -62395,10 +62391,10 @@
         <v>142</v>
       </c>
       <c r="Z523" t="s" s="2">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="AA523" t="s" s="2">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="AB523" t="s" s="2">
         <v>19</v>
@@ -62416,7 +62412,7 @@
         <v>19</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>79</v>
@@ -62433,13 +62429,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -62465,13 +62461,13 @@
         <v>172</v>
       </c>
       <c r="M524" t="s" s="2">
+        <v>1741</v>
+      </c>
+      <c r="N524" t="s" s="2">
         <v>1742</v>
       </c>
-      <c r="N524" t="s" s="2">
+      <c r="O524" t="s" s="2">
         <v>1743</v>
-      </c>
-      <c r="O524" t="s" s="2">
-        <v>1744</v>
       </c>
       <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
@@ -62500,7 +62496,7 @@
         <v>191</v>
       </c>
       <c r="Z524" t="s" s="2">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="AA524" t="s" s="2">
         <v>19</v>
@@ -62521,7 +62517,7 @@
         <v>19</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1741</v>
+        <v>1740</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>72</v>
@@ -62538,13 +62534,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -62570,14 +62566,14 @@
         <v>172</v>
       </c>
       <c r="M525" t="s" s="2">
+        <v>1746</v>
+      </c>
+      <c r="N525" t="s" s="2">
         <v>1747</v>
-      </c>
-      <c r="N525" t="s" s="2">
-        <v>1748</v>
       </c>
       <c r="O525" s="2"/>
       <c r="P525" t="s" s="2">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="Q525" t="s" s="2">
         <v>19</v>
@@ -62605,7 +62601,7 @@
         <v>191</v>
       </c>
       <c r="Z525" t="s" s="2">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="AA525" t="s" s="2">
         <v>19</v>
@@ -62626,7 +62622,7 @@
         <v>19</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>72</v>
@@ -62643,13 +62639,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -62675,13 +62671,13 @@
         <v>99</v>
       </c>
       <c r="M526" t="s" s="2">
+        <v>1751</v>
+      </c>
+      <c r="N526" t="s" s="2">
         <v>1752</v>
       </c>
-      <c r="N526" t="s" s="2">
+      <c r="O526" t="s" s="2">
         <v>1753</v>
-      </c>
-      <c r="O526" t="s" s="2">
-        <v>1754</v>
       </c>
       <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
@@ -62710,11 +62706,11 @@
         <v>142</v>
       </c>
       <c r="Z526" t="s" s="2">
+        <v>1754</v>
+      </c>
+      <c r="AA526" t="s" s="2">
         <v>1755</v>
       </c>
-      <c r="AA526" t="s" s="2">
-        <v>1756</v>
-      </c>
       <c r="AB526" t="s" s="2">
         <v>19</v>
       </c>
@@ -62731,7 +62727,7 @@
         <v>19</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>79</v>
@@ -62748,13 +62744,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -62783,11 +62779,11 @@
         <v>1565</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" t="s" s="2">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="Q527" t="s" s="2">
         <v>19</v>
@@ -62817,7 +62813,7 @@
         <v>142</v>
       </c>
       <c r="Z527" t="s" s="2">
-        <v>1760</v>
+        <v>1759</v>
       </c>
       <c r="AA527" t="s" s="2">
         <v>1569</v>
@@ -62838,7 +62834,7 @@
         <v>19</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1757</v>
+        <v>1756</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>72</v>
@@ -62855,13 +62851,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -62887,13 +62883,13 @@
         <v>172</v>
       </c>
       <c r="M528" t="s" s="2">
+        <v>1761</v>
+      </c>
+      <c r="N528" t="s" s="2">
         <v>1762</v>
       </c>
-      <c r="N528" t="s" s="2">
+      <c r="O528" t="s" s="2">
         <v>1763</v>
-      </c>
-      <c r="O528" t="s" s="2">
-        <v>1764</v>
       </c>
       <c r="P528" s="2"/>
       <c r="Q528" t="s" s="2">
@@ -62922,11 +62918,11 @@
         <v>191</v>
       </c>
       <c r="Z528" t="s" s="2">
+        <v>1764</v>
+      </c>
+      <c r="AA528" t="s" s="2">
         <v>1765</v>
       </c>
-      <c r="AA528" t="s" s="2">
-        <v>1766</v>
-      </c>
       <c r="AB528" t="s" s="2">
         <v>19</v>
       </c>
@@ -62943,7 +62939,7 @@
         <v>19</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1761</v>
+        <v>1760</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>72</v>
@@ -62960,13 +62956,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -62992,10 +62988,10 @@
         <v>152</v>
       </c>
       <c r="M529" t="s" s="2">
+        <v>1767</v>
+      </c>
+      <c r="N529" t="s" s="2">
         <v>1768</v>
-      </c>
-      <c r="N529" t="s" s="2">
-        <v>1769</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -63046,7 +63042,7 @@
         <v>19</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>72</v>
@@ -63063,13 +63059,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -63095,16 +63091,16 @@
         <v>384</v>
       </c>
       <c r="M530" t="s" s="2">
+        <v>1770</v>
+      </c>
+      <c r="N530" t="s" s="2">
         <v>1771</v>
       </c>
-      <c r="N530" t="s" s="2">
+      <c r="O530" t="s" s="2">
         <v>1772</v>
       </c>
-      <c r="O530" t="s" s="2">
+      <c r="P530" t="s" s="2">
         <v>1773</v>
-      </c>
-      <c r="P530" t="s" s="2">
-        <v>1774</v>
       </c>
       <c r="Q530" t="s" s="2">
         <v>19</v>
@@ -63153,7 +63149,7 @@
         <v>19</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1770</v>
+        <v>1769</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>72</v>
@@ -63170,13 +63166,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -63202,14 +63198,14 @@
         <v>378</v>
       </c>
       <c r="M531" t="s" s="2">
+        <v>1775</v>
+      </c>
+      <c r="N531" t="s" s="2">
         <v>1776</v>
-      </c>
-      <c r="N531" t="s" s="2">
-        <v>1777</v>
       </c>
       <c r="O531" s="2"/>
       <c r="P531" t="s" s="2">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="Q531" t="s" s="2">
         <v>19</v>
@@ -63258,7 +63254,7 @@
         <v>19</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>72</v>
@@ -63275,13 +63271,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -63307,14 +63303,14 @@
         <v>390</v>
       </c>
       <c r="M532" t="s" s="2">
+        <v>1779</v>
+      </c>
+      <c r="N532" t="s" s="2">
         <v>1780</v>
-      </c>
-      <c r="N532" t="s" s="2">
-        <v>1781</v>
       </c>
       <c r="O532" s="2"/>
       <c r="P532" t="s" s="2">
-        <v>1782</v>
+        <v>1781</v>
       </c>
       <c r="Q532" t="s" s="2">
         <v>19</v>
@@ -63363,7 +63359,7 @@
         <v>19</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>72</v>
@@ -63380,13 +63376,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -63412,10 +63408,10 @@
         <v>333</v>
       </c>
       <c r="M533" t="s" s="2">
+        <v>1783</v>
+      </c>
+      <c r="N533" t="s" s="2">
         <v>1784</v>
-      </c>
-      <c r="N533" t="s" s="2">
-        <v>1785</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -63466,7 +63462,7 @@
         <v>19</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>72</v>
@@ -63483,17 +63479,17 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
-        <v>1787</v>
+        <v>1786</v>
       </c>
       <c r="F534" s="2"/>
       <c r="G534" t="s" s="2">
@@ -63512,17 +63508,17 @@
         <v>19</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="M534" t="s" s="2">
+        <v>1787</v>
+      </c>
+      <c r="N534" t="s" s="2">
         <v>1788</v>
-      </c>
-      <c r="N534" t="s" s="2">
-        <v>1789</v>
       </c>
       <c r="O534" s="2"/>
       <c r="P534" t="s" s="2">
-        <v>1790</v>
+        <v>1789</v>
       </c>
       <c r="Q534" t="s" s="2">
         <v>19</v>
@@ -63571,7 +63567,7 @@
         <v>19</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>72</v>
@@ -63580,7 +63576,7 @@
         <v>79</v>
       </c>
       <c r="AJ534" t="s" s="2">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="AK534" t="s" s="2">
         <v>91</v>
@@ -63588,17 +63584,17 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
-        <v>1793</v>
+        <v>1792</v>
       </c>
       <c r="F535" s="2"/>
       <c r="G535" t="s" s="2">
@@ -63617,17 +63613,17 @@
         <v>80</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>644</v>
+        <v>397</v>
       </c>
       <c r="M535" t="s" s="2">
+        <v>1793</v>
+      </c>
+      <c r="N535" t="s" s="2">
         <v>1794</v>
-      </c>
-      <c r="N535" t="s" s="2">
-        <v>1795</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" t="s" s="2">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="Q535" t="s" s="2">
         <v>19</v>
@@ -63676,7 +63672,7 @@
         <v>19</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>72</v>
@@ -63685,7 +63681,7 @@
         <v>79</v>
       </c>
       <c r="AJ535" t="s" s="2">
-        <v>1791</v>
+        <v>1790</v>
       </c>
       <c r="AK535" t="s" s="2">
         <v>91</v>
@@ -63693,13 +63689,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -63722,17 +63718,17 @@
         <v>80</v>
       </c>
       <c r="L536" t="s" s="2">
+        <v>1797</v>
+      </c>
+      <c r="M536" t="s" s="2">
         <v>1798</v>
       </c>
-      <c r="M536" t="s" s="2">
+      <c r="N536" t="s" s="2">
         <v>1799</v>
-      </c>
-      <c r="N536" t="s" s="2">
-        <v>1800</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" t="s" s="2">
-        <v>1801</v>
+        <v>1800</v>
       </c>
       <c r="Q536" t="s" s="2">
         <v>19</v>
@@ -63781,7 +63777,7 @@
         <v>19</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>72</v>
@@ -63798,13 +63794,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -63830,14 +63826,14 @@
         <v>172</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1645</v>
+        <v>1644</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="O537" s="2"/>
       <c r="P537" t="s" s="2">
-        <v>1804</v>
+        <v>1803</v>
       </c>
       <c r="Q537" t="s" s="2">
         <v>19</v>
@@ -63865,11 +63861,11 @@
         <v>103</v>
       </c>
       <c r="Z537" t="s" s="2">
+        <v>1804</v>
+      </c>
+      <c r="AA537" t="s" s="2">
         <v>1805</v>
       </c>
-      <c r="AA537" t="s" s="2">
-        <v>1806</v>
-      </c>
       <c r="AB537" t="s" s="2">
         <v>19</v>
       </c>
@@ -63886,7 +63882,7 @@
         <v>19</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1802</v>
+        <v>1801</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>72</v>
@@ -63903,17 +63899,17 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
-        <v>1808</v>
+        <v>1807</v>
       </c>
       <c r="F538" s="2"/>
       <c r="G538" t="s" s="2">
@@ -63932,19 +63928,19 @@
         <v>80</v>
       </c>
       <c r="L538" t="s" s="2">
+        <v>1808</v>
+      </c>
+      <c r="M538" t="s" s="2">
         <v>1809</v>
       </c>
-      <c r="M538" t="s" s="2">
+      <c r="N538" t="s" s="2">
         <v>1810</v>
       </c>
-      <c r="N538" t="s" s="2">
+      <c r="O538" t="s" s="2">
         <v>1811</v>
       </c>
-      <c r="O538" t="s" s="2">
+      <c r="P538" t="s" s="2">
         <v>1812</v>
-      </c>
-      <c r="P538" t="s" s="2">
-        <v>1813</v>
       </c>
       <c r="Q538" t="s" s="2">
         <v>19</v>
@@ -63993,7 +63989,7 @@
         <v>19</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1807</v>
+        <v>1806</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>72</v>
@@ -64010,13 +64006,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -64042,14 +64038,14 @@
         <v>228</v>
       </c>
       <c r="M539" t="s" s="2">
+        <v>1814</v>
+      </c>
+      <c r="N539" t="s" s="2">
         <v>1815</v>
-      </c>
-      <c r="N539" t="s" s="2">
-        <v>1816</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" t="s" s="2">
-        <v>1817</v>
+        <v>1816</v>
       </c>
       <c r="Q539" t="s" s="2">
         <v>19</v>
@@ -64098,7 +64094,7 @@
         <v>19</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>72</v>
@@ -64115,13 +64111,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -64147,13 +64143,13 @@
         <v>172</v>
       </c>
       <c r="M540" t="s" s="2">
+        <v>1818</v>
+      </c>
+      <c r="N540" t="s" s="2">
         <v>1819</v>
       </c>
-      <c r="N540" t="s" s="2">
+      <c r="O540" t="s" s="2">
         <v>1820</v>
-      </c>
-      <c r="O540" t="s" s="2">
-        <v>1821</v>
       </c>
       <c r="P540" s="2"/>
       <c r="Q540" t="s" s="2">
@@ -64182,7 +64178,7 @@
         <v>191</v>
       </c>
       <c r="Z540" t="s" s="2">
-        <v>1822</v>
+        <v>1821</v>
       </c>
       <c r="AA540" t="s" s="2">
         <v>19</v>
@@ -64203,7 +64199,7 @@
         <v>19</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1818</v>
+        <v>1817</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>72</v>
@@ -64220,13 +64216,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -64252,13 +64248,13 @@
         <v>384</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="N541" t="s" s="2">
+        <v>1823</v>
+      </c>
+      <c r="O541" t="s" s="2">
         <v>1824</v>
-      </c>
-      <c r="O541" t="s" s="2">
-        <v>1825</v>
       </c>
       <c r="P541" s="2"/>
       <c r="Q541" t="s" s="2">
@@ -64308,7 +64304,7 @@
         <v>19</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1823</v>
+        <v>1822</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>72</v>
@@ -64325,13 +64321,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -64354,13 +64350,13 @@
         <v>19</v>
       </c>
       <c r="L542" t="s" s="2">
+        <v>1665</v>
+      </c>
+      <c r="M542" t="s" s="2">
         <v>1666</v>
       </c>
-      <c r="M542" t="s" s="2">
-        <v>1667</v>
-      </c>
       <c r="N542" t="s" s="2">
-        <v>1827</v>
+        <v>1826</v>
       </c>
       <c r="O542" s="2"/>
       <c r="P542" s="2"/>
@@ -64411,7 +64407,7 @@
         <v>19</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1826</v>
+        <v>1825</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>72</v>
@@ -64428,13 +64424,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -64460,10 +64456,10 @@
         <v>436</v>
       </c>
       <c r="M543" t="s" s="2">
+        <v>1828</v>
+      </c>
+      <c r="N543" t="s" s="2">
         <v>1829</v>
-      </c>
-      <c r="N543" t="s" s="2">
-        <v>1830</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -64514,7 +64510,7 @@
         <v>19</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1828</v>
+        <v>1827</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>72</v>
@@ -64531,17 +64527,17 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
-        <v>1832</v>
+        <v>1831</v>
       </c>
       <c r="F544" s="2"/>
       <c r="G544" t="s" s="2">
@@ -64560,16 +64556,16 @@
         <v>19</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>1690</v>
+        <v>1689</v>
       </c>
       <c r="M544" t="s" s="2">
+        <v>1832</v>
+      </c>
+      <c r="N544" t="s" s="2">
         <v>1833</v>
       </c>
-      <c r="N544" t="s" s="2">
+      <c r="O544" t="s" s="2">
         <v>1834</v>
-      </c>
-      <c r="O544" t="s" s="2">
-        <v>1835</v>
       </c>
       <c r="P544" s="2"/>
       <c r="Q544" t="s" s="2">
@@ -64619,7 +64615,7 @@
         <v>19</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>1831</v>
+        <v>1830</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>72</v>
@@ -64636,13 +64632,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -64668,14 +64664,14 @@
         <v>195</v>
       </c>
       <c r="M545" t="s" s="2">
+        <v>1836</v>
+      </c>
+      <c r="N545" t="s" s="2">
         <v>1837</v>
-      </c>
-      <c r="N545" t="s" s="2">
-        <v>1838</v>
       </c>
       <c r="O545" s="2"/>
       <c r="P545" t="s" s="2">
-        <v>1839</v>
+        <v>1838</v>
       </c>
       <c r="Q545" t="s" s="2">
         <v>19</v>
@@ -64724,7 +64720,7 @@
         <v>19</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1836</v>
+        <v>1835</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>72</v>
@@ -64741,13 +64737,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1840</v>
+        <v>1839</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -64844,13 +64840,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1841</v>
+        <v>1840</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -64949,13 +64945,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1842</v>
+        <v>1841</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -65056,13 +65052,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -65085,17 +65081,17 @@
         <v>19</v>
       </c>
       <c r="L549" t="s" s="2">
+        <v>1843</v>
+      </c>
+      <c r="M549" t="s" s="2">
         <v>1844</v>
       </c>
-      <c r="M549" t="s" s="2">
+      <c r="N549" t="s" s="2">
         <v>1845</v>
-      </c>
-      <c r="N549" t="s" s="2">
-        <v>1846</v>
       </c>
       <c r="O549" s="2"/>
       <c r="P549" t="s" s="2">
-        <v>1847</v>
+        <v>1846</v>
       </c>
       <c r="Q549" t="s" s="2">
         <v>19</v>
@@ -65144,7 +65140,7 @@
         <v>19</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1843</v>
+        <v>1842</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>72</v>
@@ -65161,13 +65157,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -65193,16 +65189,16 @@
         <v>333</v>
       </c>
       <c r="M550" t="s" s="2">
+        <v>1848</v>
+      </c>
+      <c r="N550" t="s" s="2">
         <v>1849</v>
       </c>
-      <c r="N550" t="s" s="2">
+      <c r="O550" t="s" s="2">
         <v>1850</v>
       </c>
-      <c r="O550" t="s" s="2">
+      <c r="P550" t="s" s="2">
         <v>1851</v>
-      </c>
-      <c r="P550" t="s" s="2">
-        <v>1852</v>
       </c>
       <c r="Q550" t="s" s="2">
         <v>19</v>
@@ -65251,7 +65247,7 @@
         <v>19</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1848</v>
+        <v>1847</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>72</v>
@@ -65268,13 +65264,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -65297,13 +65293,13 @@
         <v>19</v>
       </c>
       <c r="L551" t="s" s="2">
+        <v>1853</v>
+      </c>
+      <c r="M551" t="s" s="2">
         <v>1854</v>
       </c>
-      <c r="M551" t="s" s="2">
+      <c r="N551" t="s" s="2">
         <v>1855</v>
-      </c>
-      <c r="N551" t="s" s="2">
-        <v>1856</v>
       </c>
       <c r="O551" s="2"/>
       <c r="P551" s="2"/>
@@ -65354,7 +65350,7 @@
         <v>19</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1853</v>
+        <v>1852</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>72</v>
@@ -65371,17 +65367,17 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
-        <v>1858</v>
+        <v>1857</v>
       </c>
       <c r="F552" s="2"/>
       <c r="G552" t="s" s="2">
@@ -65403,14 +65399,14 @@
         <v>195</v>
       </c>
       <c r="M552" t="s" s="2">
+        <v>1858</v>
+      </c>
+      <c r="N552" t="s" s="2">
         <v>1859</v>
-      </c>
-      <c r="N552" t="s" s="2">
-        <v>1860</v>
       </c>
       <c r="O552" s="2"/>
       <c r="P552" t="s" s="2">
-        <v>1861</v>
+        <v>1860</v>
       </c>
       <c r="Q552" t="s" s="2">
         <v>19</v>
@@ -65459,7 +65455,7 @@
         <v>19</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1857</v>
+        <v>1856</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>72</v>
@@ -65476,13 +65472,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1862</v>
+        <v>1861</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -65579,13 +65575,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -65684,13 +65680,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1864</v>
+        <v>1863</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -65791,13 +65787,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -65823,16 +65819,16 @@
         <v>172</v>
       </c>
       <c r="M556" t="s" s="2">
+        <v>1865</v>
+      </c>
+      <c r="N556" t="s" s="2">
         <v>1866</v>
       </c>
-      <c r="N556" t="s" s="2">
+      <c r="O556" t="s" s="2">
         <v>1867</v>
       </c>
-      <c r="O556" t="s" s="2">
+      <c r="P556" t="s" s="2">
         <v>1868</v>
-      </c>
-      <c r="P556" t="s" s="2">
-        <v>1869</v>
       </c>
       <c r="Q556" t="s" s="2">
         <v>19</v>
@@ -65860,7 +65856,7 @@
         <v>191</v>
       </c>
       <c r="Z556" t="s" s="2">
-        <v>1870</v>
+        <v>1869</v>
       </c>
       <c r="AA556" t="s" s="2">
         <v>19</v>
@@ -65881,7 +65877,7 @@
         <v>19</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1865</v>
+        <v>1864</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>79</v>
@@ -65898,13 +65894,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -65927,13 +65923,13 @@
         <v>19</v>
       </c>
       <c r="L557" t="s" s="2">
+        <v>1871</v>
+      </c>
+      <c r="M557" t="s" s="2">
         <v>1872</v>
       </c>
-      <c r="M557" t="s" s="2">
+      <c r="N557" t="s" s="2">
         <v>1873</v>
-      </c>
-      <c r="N557" t="s" s="2">
-        <v>1874</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -65984,7 +65980,7 @@
         <v>19</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1871</v>
+        <v>1870</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>79</v>
@@ -66001,13 +65997,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -66033,14 +66029,14 @@
         <v>195</v>
       </c>
       <c r="M558" t="s" s="2">
+        <v>1875</v>
+      </c>
+      <c r="N558" t="s" s="2">
         <v>1876</v>
-      </c>
-      <c r="N558" t="s" s="2">
-        <v>1877</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" t="s" s="2">
-        <v>1878</v>
+        <v>1877</v>
       </c>
       <c r="Q558" t="s" s="2">
         <v>19</v>
@@ -66089,7 +66085,7 @@
         <v>19</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>72</v>
@@ -66106,13 +66102,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1879</v>
+        <v>1878</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -66209,13 +66205,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1880</v>
+        <v>1879</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -66314,13 +66310,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1881</v>
+        <v>1880</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -66421,13 +66417,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -66453,14 +66449,14 @@
         <v>172</v>
       </c>
       <c r="M562" t="s" s="2">
+        <v>1882</v>
+      </c>
+      <c r="N562" t="s" s="2">
         <v>1883</v>
-      </c>
-      <c r="N562" t="s" s="2">
-        <v>1884</v>
       </c>
       <c r="O562" s="2"/>
       <c r="P562" t="s" s="2">
-        <v>1885</v>
+        <v>1884</v>
       </c>
       <c r="Q562" t="s" s="2">
         <v>19</v>
@@ -66488,7 +66484,7 @@
         <v>191</v>
       </c>
       <c r="Z562" t="s" s="2">
-        <v>1886</v>
+        <v>1885</v>
       </c>
       <c r="AA562" t="s" s="2">
         <v>19</v>
@@ -66509,7 +66505,7 @@
         <v>19</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1882</v>
+        <v>1881</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>79</v>
@@ -66526,13 +66522,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -66629,13 +66625,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -66734,13 +66730,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -66766,16 +66762,16 @@
         <v>146</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="O565" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="P565" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="Q565" t="s" s="2">
         <v>19</v>
@@ -66824,7 +66820,7 @@
         <v>19</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>72</v>
@@ -66841,13 +66837,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -66873,16 +66869,16 @@
         <v>152</v>
       </c>
       <c r="M566" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="N566" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="O566" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="P566" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="Q566" t="s" s="2">
         <v>19</v>
@@ -66931,7 +66927,7 @@
         <v>19</v>
       </c>
       <c r="AG566" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="AH566" t="s" s="2">
         <v>72</v>
@@ -66948,13 +66944,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -66977,17 +66973,17 @@
         <v>19</v>
       </c>
       <c r="L567" t="s" s="2">
+        <v>1891</v>
+      </c>
+      <c r="M567" t="s" s="2">
         <v>1892</v>
       </c>
-      <c r="M567" t="s" s="2">
+      <c r="N567" t="s" s="2">
         <v>1893</v>
-      </c>
-      <c r="N567" t="s" s="2">
-        <v>1894</v>
       </c>
       <c r="O567" s="2"/>
       <c r="P567" t="s" s="2">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="Q567" t="s" s="2">
         <v>19</v>
@@ -67036,7 +67032,7 @@
         <v>19</v>
       </c>
       <c r="AG567" t="s" s="2">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="AH567" t="s" s="2">
         <v>79</v>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -337,7 +337,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -616,7 +616,7 @@
     <t>Physical form of the location.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/location-physical-type</t>
+    <t>http://hl7.org/fhir/ValueSet/location-physical-type|4.0.1</t>
   </si>
   <si>
     <t>Location.position</t>
@@ -707,7 +707,7 @@
     <t>Location.managingOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>Location.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Location)
+    <t xml:space="preserve">Reference(Location|4.0.1)
 </t>
   </si>
   <si>
@@ -823,7 +823,7 @@
     <t>Location.endpoint</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Endpoint)
+    <t xml:space="preserve">Reference(Endpoint|4.0.1)
 </t>
   </si>
   <si>
@@ -990,7 +990,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -1014,7 +1014,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/result_uuid</t>
+    <t>http://openelis-global.org/result_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -1108,7 +1108,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -1160,7 +1160,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -1185,7 +1185,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Observation.subject</t>
@@ -1210,7 +1210,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1230,7 +1230,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1343,7 +1343,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1372,7 +1372,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>Observation.note</t>
@@ -1410,7 +1410,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>Observation.method</t>
@@ -1431,13 +1431,13 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1453,7 +1453,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1497,7 +1497,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1538,7 +1538,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.appliesTo</t>
@@ -1559,7 +1559,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1590,7 +1590,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1606,7 +1606,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1786,7 +1786,7 @@
     <t>Specimen.identifier.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/sampleItem_uuid</t>
+    <t>http://openelis-global.org/sampleItem_uuid</t>
   </si>
   <si>
     <t>Specimen.identifier:uuid.value</t>
@@ -2068,7 +2068,7 @@
     <t>Specimen.collection.collector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -2134,7 +2134,7 @@
     <t>The  technique that is used to perform the procedure.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-collection-method|4.0.1</t>
   </si>
   <si>
     <t>Specimen.collection.bodySite</t>
@@ -2213,13 +2213,13 @@
     <t>Type indicating the technique used to process the specimen.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-processing-procedure|4.0.1</t>
   </si>
   <si>
     <t>Specimen.processing.additive</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Substance)
+    <t xml:space="preserve">Reference(Substance|4.0.1)
 </t>
   </si>
   <si>
@@ -2290,7 +2290,7 @@
     <t>Type of specimen container.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/specimen-container-type</t>
+    <t>http://hl7.org/fhir/ValueSet/specimen-container-type|4.0.1</t>
   </si>
   <si>
     <t>Specimen.container.capacity</t>
@@ -2315,7 +2315,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Substance)</t>
+Reference(Substance|4.0.1)</t>
   </si>
   <si>
     <t>Additive associated with container</t>
@@ -2476,7 +2476,7 @@
     <t>Organization.identifier:cliaNum.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_cliaNum</t>
+    <t>http://openelis-global.org/org_cliaNum</t>
   </si>
   <si>
     <t>Organization.identifier:cliaNum.value</t>
@@ -2509,7 +2509,7 @@
     <t>Organization.identifier:shortName.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_shortName</t>
+    <t>http://openelis-global.org/org_shortName</t>
   </si>
   <si>
     <t>Organization.identifier:shortName.value</t>
@@ -2542,7 +2542,7 @@
     <t>Organization.identifier:code.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_code</t>
+    <t>http://openelis-global.org/org_code</t>
   </si>
   <si>
     <t>Organization.identifier:code.value</t>
@@ -2572,7 +2572,7 @@
     <t>Organization.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/org_uuid</t>
+    <t>http://openelis-global.org/org_uuid</t>
   </si>
   <si>
     <t>Organization.identifier:uuid.value</t>
@@ -2623,7 +2623,7 @@
     <t>Used to categorize the organization.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/organization-type</t>
+    <t>http://hl7.org/fhir/ValueSet/organization-type|4.0.1</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -2959,7 +2959,7 @@
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/contactentity-type</t>
+    <t>http://hl7.org/fhir/ValueSet/contactentity-type|4.0.1</t>
   </si>
   <si>
     <t>Organization.contact.name</t>
@@ -3509,7 +3509,7 @@
     <t>DiagnosticReport.identifier.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/analysisResult_uuid</t>
+    <t>http://openelis-global.org/analysisResult_uuid</t>
   </si>
   <si>
     <t>DiagnosticReport.identifier:uuid.value</t>
@@ -3583,7 +3583,7 @@
     <t>Codes for diagnostic service sections.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections</t>
+    <t>http://hl7.org/fhir/ValueSet/diagnostic-service-sections|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticReport.code</t>
@@ -3602,7 +3602,7 @@
     <t>Codes that describe Diagnostic Reports.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/report-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/report-codes|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticReport.code.id</t>
@@ -3693,7 +3693,7 @@
 ServicePractitionerDepartmentCompanyAuthorized byDirector</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1)
 </t>
   </si>
   <si>
@@ -3770,7 +3770,7 @@
     <t>DiagnosticReport.imagingStudy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ImagingStudy)
+    <t xml:space="preserve">Reference(ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -3826,7 +3826,7 @@
     <t>DiagnosticReport.media.link</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Media)
+    <t xml:space="preserve">Reference(Media|4.0.1)
 </t>
   </si>
   <si>
@@ -3864,7 +3864,7 @@
     <t>Diagnosis codes provided as adjuncts to the report.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>DiagnosticReport.presentedForm</t>
@@ -3997,7 +3997,7 @@
     <t>Patient.identifier:nationalid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_nationalId</t>
+    <t>http://openelis-global.org/pat_nationalId</t>
   </si>
   <si>
     <t>Patient.identifier:nationalid.value</t>
@@ -4030,7 +4030,7 @@
     <t>Patient.identifier:subjectnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_subjectNumber</t>
+    <t>http://openelis-global.org/pat_subjectNumber</t>
   </si>
   <si>
     <t>Patient.identifier:subjectnumber.value</t>
@@ -4063,7 +4063,7 @@
     <t>Patient.identifier:stnumber.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_stNumber</t>
+    <t>http://openelis-global.org/pat_stNumber</t>
   </si>
   <si>
     <t>Patient.identifier:stnumber.value</t>
@@ -4096,7 +4096,7 @@
     <t>Patient.identifier:guid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_guid</t>
+    <t>http://openelis-global.org/pat_guid</t>
   </si>
   <si>
     <t>Patient.identifier:guid.value</t>
@@ -4126,7 +4126,7 @@
     <t>Patient.identifier:uuid.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/pat_uuid</t>
+    <t>http://openelis-global.org/pat_uuid</t>
   </si>
   <si>
     <t>Patient.identifier:uuid.value</t>
@@ -4259,7 +4259,7 @@
     <t>The domestic partnership status of a person.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/marital-status</t>
+    <t>http://hl7.org/fhir/ValueSet/marital-status|4.0.1</t>
   </si>
   <si>
     <t>Patient.multipleBirth[x]</t>
@@ -4342,7 +4342,7 @@
     <t>The nature of the relationship between a patient and a contact person for that patient.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship</t>
+    <t>http://hl7.org/fhir/ValueSet/patient-contactrelationship|4.0.1</t>
   </si>
   <si>
     <t>Patient.contact.name</t>
@@ -4473,7 +4473,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|Practitioner|PractitionerRole)
+    <t xml:space="preserve">Reference(Organization|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1)
 </t>
   </si>
   <si>
@@ -4532,7 +4532,7 @@
     <t>Patient.link.other</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(Patient|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -4664,7 +4664,7 @@
     <t>ServiceRequest.identifier.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/analysis_uuid</t>
+    <t>http://openelis-global.org/analysis_uuid</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:uuid.value</t>
@@ -4706,7 +4706,7 @@
     <t>ServiceRequest.identifier:labNo.system</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/samp_labNo</t>
+    <t>http://openelis-global.org/samp_labNo</t>
   </si>
   <si>
     <t>ServiceRequest.identifier:labNo.value</t>
@@ -4721,7 +4721,7 @@
     <t>ServiceRequest.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition|PlanDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -4753,7 +4753,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|ServiceRequest|MedicationRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|ServiceRequest|4.0.1|MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -4770,7 +4770,7 @@
 priorrenewed order</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(ServiceRequest)
+    <t xml:space="preserve">Reference(ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -4853,7 +4853,7 @@
     <t>Classification of the requested service.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-category</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-category|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.priority</t>
@@ -4911,7 +4911,7 @@
     <t>Codes for tests or services that can be carried out by a designated individual, organization or healthcare service.  For laboratory, LOINC is  (preferred)[http://build.fhir.org/terminologies.html#preferred].</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-code</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-code|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.code.id</t>
@@ -4966,7 +4966,7 @@
     <t>Codified order entry details which are based on order context.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail</t>
+    <t>http://hl7.org/fhir/ValueSet/servicerequest-orderdetail|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">prr-1
@@ -5044,7 +5044,7 @@
     <t>A coded concept identifying the pre-condition that should hold prior to performing a procedure.  For example "pain", "on flare-up", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medication-as-needed-reason|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.authoredOn</t>
@@ -5095,7 +5095,7 @@
     <t>Indicates specific responsibility of an individual within the care team, such as "Primary physician", "Team coordinator", "Caregiver", etc.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/participant-role|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.performer</t>
@@ -5105,7 +5105,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|HealthcareService|Patient|Device|RelatedPerson)
+    <t xml:space="preserve">Reference(Practitioner|4.0.1|PractitionerRole|4.0.1|Organization|4.0.1|CareTeam|4.0.1|HealthcareService|4.0.1|Patient|4.0.1|Device|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -5151,13 +5151,13 @@
     <t>Diagnosis or problem codes justifying the reason for requesting the service investigation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/procedure-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/procedure-reason|4.0.1</t>
   </si>
   <si>
     <t>ServiceRequest.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation|DiagnosticReport|DocumentReference)
+    <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1|DiagnosticReport|4.0.1|DocumentReference|4.0.1)
 </t>
   </si>
   <si>
@@ -5173,7 +5173,7 @@
     <t>ServiceRequest.insurance</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Coverage|ClaimResponse)
+    <t xml:space="preserve">Reference(Coverage|4.0.1|ClaimResponse|4.0.1)
 </t>
   </si>
   <si>
@@ -5248,7 +5248,7 @@
     <t>ServiceRequest.relevantHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.0.1)
 </t>
   </si>
   <si>
@@ -5330,7 +5330,7 @@
     <t>Task.instantiatesCanonical</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ActivityDefinition)
+    <t xml:space="preserve">canonical(ActivityDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -5376,7 +5376,7 @@
     <t>Task.partOf</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Task)
+    <t xml:space="preserve">Reference(Task|4.0.1)
 </t>
   </si>
   <si>
@@ -5483,7 +5483,7 @@
     <t>Codes to identify what the task involves.  These will typically be specific to a particular workflow.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/task-code</t>
+    <t>http://hl7.org/fhir/ValueSet/task-code|4.0.1</t>
   </si>
   <si>
     <t>Task.description</t>
@@ -5582,7 +5582,7 @@
     <t>Task.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|Organization|Patient|Practitioner|PractitionerRole|RelatedPerson)
+    <t xml:space="preserve">Reference(Device|4.0.1|Organization|4.0.1|Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1)
 </t>
   </si>
   <si>
@@ -5607,7 +5607,7 @@
     <t>The type(s) of task performers allowed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/performer-role</t>
+    <t>http://hl7.org/fhir/ValueSet/performer-role|4.0.1</t>
   </si>
   <si>
     <t>Task.owner</t>
@@ -5755,7 +5755,7 @@
     <t>Task.restriction.recipient</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Patient|Practitioner|PractitionerRole|RelatedPerson|Group|Organization)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1|PractitionerRole|4.0.1|RelatedPerson|4.0.1|Group|4.0.1|Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -7420,7 +7420,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="42.56640625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="36.7890625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="34.26953125" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="15.13671875" customWidth="true" bestFit="true"/>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/all-profiles.xlsx
+++ b/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -24676,10 +24676,10 @@
       </c>
       <c r="F165" s="2"/>
       <c r="G165" t="s" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H165" t="s" s="2">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="I165" t="s" s="2">
         <v>19</v>
@@ -25506,7 +25506,7 @@
       </c>
       <c r="F173" s="2"/>
       <c r="G173" t="s" s="2">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H173" t="s" s="2">
         <v>79</v>
